--- a/stories/arbres/TREE-EMO-009.xlsx
+++ b/stories/arbres/TREE-EMO-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Au bord de la mer, Hugo voit Sami avec un grand seau. Hugo voudrait le même. La poitrine se serre. Les mains restent près du corps. Maman est sur la serviette. Papa cherche un galet. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Au bord de la mer, Hugo voit Sami avec un grand seau. Hugo voudrait le même. La poitrine se serre. Les mains restent près du corps. Maman est sur la serviette. Papa cherche un galet. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Au bord de la mer, Hugo voit Sami avec un grand seau. Hugo voudrait le même. La poitrine se serre. Les mains restent près du corps. Maman est sur la serviette. Papa cherche un galet. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le chat a un jouet. Hugo voudrait le même. Il est jaloux. C'est le chat. Un cube tape un autre cube, doucement. Hugo s'approche, sans courir. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Le chat a un jouet. Hugo voudrait le même. Il est jaloux. C'est le chat. Un cube tape un autre cube, doucement. Hugo s'approche, sans courir. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat a un jouet. Hugo voudrait le même. Il est jaloux. C'est le chat. Un cube tape un autre cube, doucement. Hugo s'approche, sans courir. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1861,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec le chat.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1851,7 +1890,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo retient le geste. Il respire.</t>
+          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo retient le geste. Il respire.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1993,6 +2032,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo retient le geste. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2254,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le bac à sable, après le chat. La corde de la balançoire bouge. On parle du bac à sable. Hugo écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le bac à sable, après le chat. La corde de la balançoire bouge. On parle du bac à sable. Hugo écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2392,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le bac à sable, après le chat. La corde de la balançoire bouge. On parle du bac à sable. Hugo écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2588,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2617,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le rouge un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+          <t>Hugo rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le rouge un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2755,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo garde le rouge un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2924,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2953,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On écoute le silence une seconde. Hugo est assis. On gardu geste.</t>
+          <t>Hugo rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On écoute le silence une seconde. Hugo est assis. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3091,13 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On écoute le silence une seconde.
+narrateur|Hugo est assis. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3260,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,7 +3289,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
+          <t>Hugo rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3341,6 +3427,13 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3596,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3625,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le toboggan, après le chat. Le banc est tiède. Hugo choisit le toboggan. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le toboggan, après le chat. Le banc est tiède. Hugo choisit le toboggan. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3763,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le toboggan, après le chat. Le banc est tiède. Hugo choisit le toboggan. Papa n'est pas loin. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3959,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3988,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On respire.</t>
+          <t>Hugo rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4126,13 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo dit merci à maman. Papa sourit. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4295,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4203,7 +4324,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On laisse bleu à sa place. Hugo est près de maman. Merci, et au dodo bientôt.</t>
+          <t>Hugo rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On laisse bleu à sa place. Hugo est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4341,6 +4462,13 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. On laisse bleu à sa place.
+narrateur|Hugo est près de maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4631,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4660,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+          <t>Hugo rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4798,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4967,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4996,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi les balançoires, après le chat. La cuillère tinte. Avec les balançoires, Hugo ralentit. Il écoute maman. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi les balançoires, après le chat. La cuillère tinte. Avec les balançoires, Hugo ralentit. Il écoute maman. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5134,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les balançoires, après le chat. La cuillère tinte. Avec les balançoires, Hugo ralentit. Il écoute maman. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5330,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5203,7 +5359,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Maman dit : je t'ai entendu. Papa aussi. On se serre un peu.</t>
+          <t>Hugo rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5341,6 +5497,13 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5666,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5527,7 +5695,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose bleu et va vers maman. On rentre.</t>
+          <t>Hugo rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose bleu et va vers maman. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5665,6 +5833,13 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose bleu et va vers maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +6002,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5851,7 +6031,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le vert un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
+          <t>Hugo rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le vert un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5989,6 +6169,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo garde le vert un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6338,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6367,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Le chien a un bâton. Hugo voudrait le même. Il est jaloux. Hugo s'occupe du chien. Le pain croustille. Maman sourit. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Le chien a un bâton. Hugo voudrait le même. Il est jaloux. Hugo s'occupe du chien. Le pain croustille. Maman sourit. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6505,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien a un bâton. Hugo voudrait le même. Il est jaloux. Hugo s'occupe du chien. Le pain croustille. Maman sourit. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6491,6 +6689,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6515,7 +6718,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo répète le mot. Maman hoche la tête.</t>
+          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6657,6 +6860,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7053,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7082,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le bac à sable, après le chien. Le sable est un peu frais. Le bac à sable reste à sa place. Hugo aussi. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le bac à sable, après le chien. Le sable est un peu frais. Le bac à sable reste à sa place. Hugo aussi. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7220,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le bac à sable, après le chien. Le sable est un peu frais. Le bac à sable reste à sa place. Hugo aussi. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7416,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7445,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. On se dit à plus tard.</t>
+          <t>Hugo rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7583,13 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7752,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7543,7 +7781,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le bleu un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+          <t>Hugo rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le bleu un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7681,6 +7919,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo garde le bleu un instant. Puis il reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8088,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7867,7 +8117,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On gardu geste.</t>
+          <t>Hugo rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8005,6 +8255,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo dit merci à maman. Papa sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8424,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8191,7 +8453,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le toboggan, après le chien. Un grillon chante, tout petit. Près du toboggan, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le toboggan, après le chien. Un grillon chante, tout petit. Près du toboggan, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8329,6 +8591,12 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le toboggan, après le chien. Un grillon chante, tout petit. Près du toboggan, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8787,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8543,7 +8816,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
+          <t>Hugo rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8681,6 +8954,13 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9123,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8867,7 +9152,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo boit une gorgée. Il se sent plus léger. On respire.</t>
+          <t>Hugo rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo boit une gorgée. Il se sent plus léger. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9005,6 +9290,13 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo boit une gorgée. Il se sent plus léger. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9459,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9191,7 +9488,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le vert un instant. Puis il reprend, calme. Merci, et au dodo bientôt.</t>
+          <t>Hugo rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo garde le vert un instant. Puis il reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9329,6 +9626,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo garde le vert un instant. Puis il reprend, calme. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9795,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9515,7 +9824,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi les balançoires, après le chien. Le lait est tiède. Hugo s'installe avec les balançoires. Maman reste à portée de voix. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi les balançoires, après le chien. Le lait est tiède. Hugo s'installe avec les balançoires. Maman reste à portée de voix. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9653,6 +9962,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les balançoires, après le chien. Le lait est tiède. Hugo s'installe avec les balançoires. Maman reste à portée de voix. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10158,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10187,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose rouge et va vers maman. Le jeu peut recommencer.</t>
+          <t>Hugo rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose rouge et va vers maman. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10325,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose rouge et va vers maman. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10494,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10191,7 +10523,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On se serre un peu.</t>
+          <t>Hugo rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10329,6 +10661,13 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo dit merci à maman. Papa sourit. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10830,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10515,7 +10859,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo boit une gorgée. Il se sent plus léger. On rentre.</t>
+          <t>Hugo rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo boit une gorgée. Il se sent plus léger. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10653,6 +10997,13 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo boit une gorgée. Il se sent plus léger. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11166,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11195,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>La poule a du grain. Hugo voudrait s'en occuper. Il est jaloux. Voilà la poule. Un chat miaule une seule fois. Hugo pose les pieds par terre, près de maman. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>La poule a du grain. Hugo voudrait s'en occuper. Il est jaloux. Voilà la poule. Un chat miaule une seule fois. Hugo pose les pieds par terre, près de maman. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11333,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|La poule a du grain. Hugo voudrait s'en occuper. Il est jaloux. Voilà la poule. Un chat miaule une seule fois. Hugo pose les pieds par terre, près de maman. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11155,6 +11517,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11179,7 +11546,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose les pieds par terre. On continue, tout calme.</t>
+          <t>Oui. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11321,6 +11688,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11881,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11531,7 +11910,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le bac à sable, après la poule. Ça sent le savon de maman. Près du bac à sable, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le bac à sable, après la poule. Ça sent le savon de maman. Près du bac à sable, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11669,6 +12048,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le bac à sable, après la poule. Ça sent le savon de maman. Près du bac à sable, Hugo prend le temps. Pas de course. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12244,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11883,7 +12273,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose rouge et va vers maman. La journée continue, tout doux.</t>
+          <t>Hugo rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose rouge et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12021,6 +12411,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose rouge et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12580,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12207,7 +12609,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. On se dit à plus tard.</t>
+          <t>Hugo rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12345,6 +12747,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo nomme encore le mot, tout bas. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12916,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12531,7 +12945,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le soleil est encore là.</t>
+          <t>Hugo rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12669,6 +13083,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo serre la main de maman, tout doux. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13252,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12855,7 +13281,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le toboggan, après la poule. Le pain croustille. Hugo range un peu autour du toboggan. Il respire. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi le toboggan, après la poule. Le pain croustille. Hugo range un peu autour du toboggan. Il respire. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12993,6 +13419,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le toboggan, après la poule. Le pain croustille. Hugo range un peu autour du toboggan. Il respire. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13615,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13644,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. On gardu geste.</t>
+          <t>Hugo rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13782,13 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo serre la main de maman, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13951,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13531,7 +13980,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose bleu et va vers maman. Papa et maman sont là.</t>
+          <t>Hugo rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose bleu et va vers maman. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13669,6 +14118,13 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose bleu et va vers maman. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14287,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13855,7 +14316,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. On respire.</t>
+          <t>Hugo rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13993,6 +14454,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo nomme encore le mot, tout bas. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14623,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14179,7 +14652,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi les balançoires, après la poule. La corde de la balançoire bouge. Hugo attend près des balançoires. Il ne prend pas de force. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+          <t>Hugo a choisi les balançoires, après la poule. La corde de la balançoire bouge. Hugo attend près des balançoires. Il ne prend pas de force. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14317,6 +14790,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les balançoires, après la poule. La corde de la balançoire bouge. Hugo attend près des balançoires. Il ne prend pas de force. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14507,6 +14986,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14531,7 +15015,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+          <t>Hugo rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14669,6 +15153,13 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15322,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14855,7 +15351,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+          <t>Hugo rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14993,6 +15489,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15658,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15179,7 +15687,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. Hugo se sent jaloux. La poitrine est serrée. Hugo dit : je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose vert et va vers maman. On se serre un peu.</t>
+          <t>Hugo rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. Hugo se sent jaloux. La poitrine est serrée. Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force. Hugo pose vert et va vers maman. On se serre un peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15317,6 +15825,13 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. Hugo se sent jaloux. La poitrine est serrée.
+enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.
+narrateur|Hugo pose vert et va vers maman. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15994,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +16017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16090,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-009.xlsx
+++ b/stories/arbres/TREE-EMO-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1513,6 +1519,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1694,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec le chat.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
 narrateur|Hugo retient le geste. Il respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2244,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2413,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2609,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2762,6 +2779,7 @@
 narrateur|Hugo garde le rouge un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2929,6 +2947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3117,7 @@
 narrateur|Hugo est assis. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3455,7 @@
 narrateur|Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3623,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3769,6 +3792,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3964,6 +3988,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4133,6 +4158,7 @@
 narrateur|Hugo dit merci à maman. Papa sourit. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4300,6 +4326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4469,6 +4496,7 @@
 narrateur|Hugo est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4636,6 +4664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4805,6 +4834,7 @@
 narrateur|Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4972,6 +5002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5140,6 +5171,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5335,6 +5367,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5504,6 +5537,7 @@
 maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5671,6 +5705,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5840,6 +5875,7 @@
 narrateur|Hugo pose bleu et va vers maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6007,6 +6043,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6176,6 +6213,7 @@
 narrateur|Hugo garde le vert un instant. Puis il reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6343,6 +6381,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6511,6 +6550,11 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6692,6 +6736,11 @@
       <c r="AW33" t="inlineStr">
         <is>
           <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec le chien.</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -6867,6 +6916,7 @@
 narrateur|Hugo répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7058,6 +7108,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7226,6 +7277,11 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7421,6 +7477,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7590,6 +7647,11 @@
 narrateur|Hugo serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7757,6 +7819,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7926,6 +7989,11 @@
 narrateur|Hugo garde le bleu un instant. Puis il reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8093,6 +8161,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8262,6 +8331,11 @@
 narrateur|Hugo dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8429,6 +8503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8597,6 +8672,11 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8792,6 +8872,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8961,6 +9042,11 @@
 narrateur|Hugo nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9128,6 +9214,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9297,6 +9384,11 @@
 narrateur|Hugo boit une gorgée. Il se sent plus léger. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9464,6 +9556,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9633,6 +9726,11 @@
 narrateur|Hugo garde le vert un instant. Puis il reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9800,6 +9898,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9968,6 +10067,11 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10163,6 +10267,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10332,6 +10437,11 @@
 narrateur|Hugo pose rouge et va vers maman. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10499,6 +10609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10668,6 +10779,11 @@
 narrateur|Hugo dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10835,6 +10951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11004,6 +11121,11 @@
 narrateur|Hugo boit une gorgée. Il se sent plus léger. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11171,6 +11293,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11339,6 +11462,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11522,6 +11646,7 @@
           <t>narrateur|Hugo veut le même jouet. Que fait-on ? Avec la poule.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11695,6 +11820,7 @@
 narrateur|Hugo pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11886,6 +12012,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12054,6 +12181,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12249,6 +12377,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12418,6 +12547,7 @@
 narrateur|Hugo pose rouge et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12585,6 +12715,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12754,6 +12885,7 @@
 narrateur|Hugo nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12921,6 +13053,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13090,6 +13223,7 @@
 narrateur|Hugo serre la main de maman, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13257,6 +13391,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13425,6 +13560,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13620,6 +13756,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13789,6 +13926,7 @@
 narrateur|Hugo serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13956,6 +14094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14125,6 +14264,7 @@
 narrateur|Hugo pose bleu et va vers maman. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14292,6 +14432,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14461,6 +14602,7 @@
 narrateur|Hugo nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14628,6 +14770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14796,6 +14939,7 @@
 enfant-m|Je suis jaloux. Il demande un tour. Il attend. Il ne prend pas de force.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14991,6 +15135,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15160,6 +15305,7 @@
 narrateur|Hugo nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15327,6 +15473,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15496,6 +15643,7 @@
 narrateur|Hugo serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15663,6 +15811,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15832,6 +15981,7 @@
 narrateur|Hugo pose vert et va vers maman. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15999,6 +16149,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16017,7 +16168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16097,6 +16248,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16111,7 +16276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16298,6 +16463,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
